--- a/fixtures/enterprise-mixed/office/book.xlsx
+++ b/fixtures/enterprise-mixed/office/book.xlsx
@@ -1,8 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="1" r:id="rId1"/>
+    <sheet name="Prices" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="2">
+      <c r="B2">
+        <f>Prices!A1</f>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>